--- a/code/data/combined/cmb+pelg+jmul-lcdm-fixed.xlsx
+++ b/code/data/combined/cmb+pelg+jmul-lcdm-fixed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,22 +467,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39309903.71068209</v>
+        <v>47085114.32038893</v>
       </c>
       <c r="C2" t="n">
-        <v>-134472624.5755765</v>
+        <v>-157261959.8939874</v>
       </c>
       <c r="D2" t="n">
-        <v>40498344.88890553</v>
+        <v>49329327.98623294</v>
       </c>
       <c r="E2" t="n">
-        <v>-328826.7714409353</v>
+        <v>-398414.6567616926</v>
       </c>
       <c r="F2" t="n">
-        <v>-1339492.473710932</v>
+        <v>-1360014.49801253</v>
       </c>
       <c r="G2" t="n">
-        <v>879085.3645679437</v>
+        <v>1128429.193533648</v>
       </c>
     </row>
     <row r="3">
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-134472624.5755923</v>
+        <v>-157261959.8939397</v>
       </c>
       <c r="C3" t="n">
-        <v>887787810.5290097</v>
+        <v>950153575.5638416</v>
       </c>
       <c r="D3" t="n">
-        <v>-89236526.53143081</v>
+        <v>-117099218.5629257</v>
       </c>
       <c r="E3" t="n">
-        <v>15622280.82639995</v>
+        <v>16778104.85918606</v>
       </c>
       <c r="F3" t="n">
-        <v>6725763.597952195</v>
+        <v>6809926.534649754</v>
       </c>
       <c r="G3" t="n">
-        <v>-3830849.072265358</v>
+        <v>-4709260.179887882</v>
       </c>
     </row>
     <row r="4">
@@ -517,22 +517,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40498344.88890427</v>
+        <v>49329327.98623738</v>
       </c>
       <c r="C4" t="n">
-        <v>-89236526.53141057</v>
+        <v>-117099218.5629919</v>
       </c>
       <c r="D4" t="n">
-        <v>48990351.07576518</v>
+        <v>58628444.20290758</v>
       </c>
       <c r="E4" t="n">
-        <v>921795.3901476359</v>
+        <v>891559.1366383312</v>
       </c>
       <c r="F4" t="n">
-        <v>-954046.0478055417</v>
+        <v>-991365.5991984552</v>
       </c>
       <c r="G4" t="n">
-        <v>971974.4851704334</v>
+        <v>1239887.704722955</v>
       </c>
     </row>
     <row r="5">
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-328826.7714415027</v>
+        <v>-398414.656759794</v>
       </c>
       <c r="C5" t="n">
-        <v>15622280.82640206</v>
+        <v>16778104.8591807</v>
       </c>
       <c r="D5" t="n">
-        <v>921795.390147046</v>
+        <v>891559.1366404236</v>
       </c>
       <c r="E5" t="n">
-        <v>1030767.846398863</v>
+        <v>1134894.161580558</v>
       </c>
       <c r="F5" t="n">
-        <v>29917.84075137741</v>
+        <v>45279.17529121712</v>
       </c>
       <c r="G5" t="n">
-        <v>-77271.80251377253</v>
+        <v>-86085.71996796312</v>
       </c>
     </row>
     <row r="6">
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1339492.473710893</v>
+        <v>-1360014.498013485</v>
       </c>
       <c r="C6" t="n">
-        <v>6725763.597950936</v>
+        <v>6809926.534653664</v>
       </c>
       <c r="D6" t="n">
-        <v>-954046.0478055112</v>
+        <v>-991365.5991993791</v>
       </c>
       <c r="E6" t="n">
-        <v>29917.84075132381</v>
+        <v>45279.17529124759</v>
       </c>
       <c r="F6" t="n">
-        <v>637642.8265049607</v>
+        <v>649399.2715859185</v>
       </c>
       <c r="G6" t="n">
-        <v>103899.4427337249</v>
+        <v>103298.4894198903</v>
       </c>
     </row>
     <row r="7">
@@ -592,22 +592,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>879085.3645680614</v>
+        <v>1128429.193533176</v>
       </c>
       <c r="C7" t="n">
-        <v>-3830849.072265576</v>
+        <v>-4709260.179887714</v>
       </c>
       <c r="D7" t="n">
-        <v>971974.4851705788</v>
+        <v>1239887.704722319</v>
       </c>
       <c r="E7" t="n">
-        <v>-77271.80251376696</v>
+        <v>-86085.71996801152</v>
       </c>
       <c r="F7" t="n">
-        <v>103899.4427337131</v>
+        <v>103298.4894199226</v>
       </c>
       <c r="G7" t="n">
-        <v>66769.24939534163</v>
+        <v>75396.24381573973</v>
       </c>
     </row>
   </sheetData>

--- a/code/data/combined/cmb+pelg+jmul-lcdm-fixed.xlsx
+++ b/code/data/combined/cmb+pelg+jmul-lcdm-fixed.xlsx
@@ -467,22 +467,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47085114.32038893</v>
+        <v>43671284.56690902</v>
       </c>
       <c r="C2" t="n">
-        <v>-157261959.8939874</v>
+        <v>-146032037.9518806</v>
       </c>
       <c r="D2" t="n">
-        <v>49329327.98623294</v>
+        <v>45623756.26109675</v>
       </c>
       <c r="E2" t="n">
-        <v>-398414.6567616926</v>
+        <v>-379416.153900772</v>
       </c>
       <c r="F2" t="n">
-        <v>-1360014.49801253</v>
+        <v>-1334633.657279041</v>
       </c>
       <c r="G2" t="n">
-        <v>1128429.193533648</v>
+        <v>1020578.406345851</v>
       </c>
     </row>
     <row r="3">
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-157261959.8939397</v>
+        <v>-146032037.9518366</v>
       </c>
       <c r="C3" t="n">
-        <v>950153575.5638416</v>
+        <v>876730590.5466701</v>
       </c>
       <c r="D3" t="n">
-        <v>-117099218.5629257</v>
+        <v>-109841979.5999176</v>
       </c>
       <c r="E3" t="n">
-        <v>16778104.85918606</v>
+        <v>15993899.89060147</v>
       </c>
       <c r="F3" t="n">
-        <v>6809926.534649754</v>
+        <v>6606462.467108841</v>
       </c>
       <c r="G3" t="n">
-        <v>-4709260.179887882</v>
+        <v>-4341449.679964654</v>
       </c>
     </row>
     <row r="4">
@@ -517,22 +517,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49329327.98623738</v>
+        <v>45623756.26110112</v>
       </c>
       <c r="C4" t="n">
-        <v>-117099218.5629919</v>
+        <v>-109841979.5999781</v>
       </c>
       <c r="D4" t="n">
-        <v>58628444.20290758</v>
+        <v>53932634.04734841</v>
       </c>
       <c r="E4" t="n">
-        <v>891559.1366383312</v>
+        <v>816073.8811664864</v>
       </c>
       <c r="F4" t="n">
-        <v>-991365.5991984552</v>
+        <v>-974232.5062266582</v>
       </c>
       <c r="G4" t="n">
-        <v>1239887.704722955</v>
+        <v>1124804.266927253</v>
       </c>
     </row>
     <row r="5">
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-398414.656759794</v>
+        <v>-379416.1538989324</v>
       </c>
       <c r="C5" t="n">
-        <v>16778104.8591807</v>
+        <v>15993899.89059567</v>
       </c>
       <c r="D5" t="n">
-        <v>891559.1366404236</v>
+        <v>816073.8811683876</v>
       </c>
       <c r="E5" t="n">
-        <v>1134894.161580558</v>
+        <v>1110110.422566251</v>
       </c>
       <c r="F5" t="n">
-        <v>45279.17529121712</v>
+        <v>48716.74950023205</v>
       </c>
       <c r="G5" t="n">
-        <v>-86085.71996796312</v>
+        <v>-84279.01038145821</v>
       </c>
     </row>
     <row r="6">
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1360014.498013485</v>
+        <v>-1334633.657279229</v>
       </c>
       <c r="C6" t="n">
-        <v>6809926.534653664</v>
+        <v>6606462.467111263</v>
       </c>
       <c r="D6" t="n">
-        <v>-991365.5991993791</v>
+        <v>-974232.5062266412</v>
       </c>
       <c r="E6" t="n">
-        <v>45279.17529124759</v>
+        <v>48716.74950030506</v>
       </c>
       <c r="F6" t="n">
-        <v>649399.2715859185</v>
+        <v>634464.5000966497</v>
       </c>
       <c r="G6" t="n">
-        <v>103298.4894198903</v>
+        <v>102551.1391833265</v>
       </c>
     </row>
     <row r="7">
@@ -592,22 +592,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1128429.193533176</v>
+        <v>1020578.406345584</v>
       </c>
       <c r="C7" t="n">
-        <v>-4709260.179887714</v>
+        <v>-4341449.679964644</v>
       </c>
       <c r="D7" t="n">
-        <v>1239887.704722319</v>
+        <v>1124804.266926892</v>
       </c>
       <c r="E7" t="n">
-        <v>-86085.71996801152</v>
+        <v>-84279.01038149124</v>
       </c>
       <c r="F7" t="n">
-        <v>103298.4894199226</v>
+        <v>102551.1391833405</v>
       </c>
       <c r="G7" t="n">
-        <v>75396.24381573973</v>
+        <v>71761.94659693741</v>
       </c>
     </row>
   </sheetData>
